--- a/app/doc/column/PDA컬럼정의_SGI.xlsx
+++ b/app/doc/column/PDA컬럼정의_SGI.xlsx
@@ -4,6 +4,8 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="VW_PDA_WID_LIST" sheetId="1" r:id="rId1"/>
+    <sheet name="VW_PDA_WID_HOMEPLUS_LIST" sheetId="2" r:id="rId2"/>
+    <sheet name="VW_PDA_WID_LIST_LOTTE" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -32,9 +34,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -424,7 +425,7 @@
         <v>VW_PDA_WID_LIST</v>
       </c>
       <c r="I3" t="str">
-        <v>품목명 : PDA 샘플데이터</v>
+        <v>품목명 : 호주산 척아이롤</v>
       </c>
     </row>
     <row r="4">
@@ -457,8 +458,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>0</v>
+      <c r="A5" t="str">
+        <v>-</v>
       </c>
       <c r="B5" t="str">
         <v>GI_H_ID</v>
@@ -472,16 +473,16 @@
       <c r="E5" t="str">
         <v>미사용(로컬DB저장)</v>
       </c>
-      <c r="F5" t="str">
-        <v>v28에서 로컬DB 삭제됨 (미사용)</v>
-      </c>
       <c r="G5" t="str">
         <v>SM_출고머리.SEQ</v>
       </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="str">
         <v>GI_D_ID</v>
@@ -501,10 +502,13 @@
       <c r="G6" t="str">
         <v>SM_출고상세.SEQ</v>
       </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>2</v>
+      <c r="A7" t="str">
+        <v>-</v>
       </c>
       <c r="B7" t="str">
         <v>EOI_ID</v>
@@ -518,16 +522,16 @@
       <c r="E7" t="str">
         <v>미사용(로컬DB저장)</v>
       </c>
-      <c r="F7" t="str">
-        <v>v28에서 로컬DB 삭제됨 (미사용)</v>
-      </c>
       <c r="G7" t="str">
         <v>SM_마트사발주이마트.SEQ</v>
       </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" t="str">
         <v>ITEM_CODE</v>
@@ -553,7 +557,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9" t="str">
         <v>ITEM_NAME</v>
@@ -574,12 +578,12 @@
         <v>CO_품목코드.제품명</v>
       </c>
       <c r="I9" t="str">
-        <v>PDA 샘플데이터</v>
+        <v>호주산 척아이롤</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B10" t="str">
         <v>EMARTITEM_CODE</v>
@@ -599,13 +603,13 @@
       <c r="G10" t="str">
         <v>CO_매출처품목코드매핑.거래처제품코드</v>
       </c>
-      <c r="I10">
-        <v>2492480000000</v>
+      <c r="I10" t="str">
+        <v>2800010000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B11" t="str">
         <v>EMARTITEM</v>
@@ -626,12 +630,12 @@
         <v>CO_매출처품목코드매핑.거래처제품명</v>
       </c>
       <c r="I11" t="str">
-        <v>PDA 샘플데이터(거래처제품명)</v>
+        <v>호주산 척아이롤(냉장)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B12" t="str">
         <v>GI_REQ_PKG</v>
@@ -651,13 +655,13 @@
       <c r="G12" t="str">
         <v>SM_출고상세.출고수량</v>
       </c>
-      <c r="I12">
-        <v>60</v>
+      <c r="I12" t="str">
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B13" t="str">
         <v>GI_REQ_QTY</v>
@@ -677,13 +681,13 @@
       <c r="G13" t="str">
         <v>SM_출고상세.출고중량</v>
       </c>
-      <c r="I13">
-        <v>60</v>
+      <c r="I13" t="str">
+        <v>100.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>9</v>
+      <c r="A14" t="str">
+        <v>-</v>
       </c>
       <c r="B14" t="str">
         <v>AMOUNT</v>
@@ -697,16 +701,13 @@
       <c r="E14" t="str">
         <v>미사용</v>
       </c>
-      <c r="F14" t="str">
-        <v>v28에서 로컬DB 삭제됨 (미사용)</v>
-      </c>
       <c r="G14" t="str">
         <v>X</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>10</v>
+      <c r="A15" t="str">
+        <v>-</v>
       </c>
       <c r="B15" t="str">
         <v>GOODS_R_ID</v>
@@ -720,16 +721,13 @@
       <c r="E15" t="str">
         <v>미사용</v>
       </c>
-      <c r="F15" t="str">
-        <v>v28에서 로컬DB 삭제됨 (미사용)</v>
-      </c>
       <c r="G15" t="str">
         <v>X</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>11</v>
+      <c r="A16" t="str">
+        <v>-</v>
       </c>
       <c r="B16" t="str">
         <v>GR_REF_NO</v>
@@ -743,16 +741,13 @@
       <c r="E16" t="str">
         <v>미사용</v>
       </c>
-      <c r="F16" t="str">
-        <v>v28에서 로컬DB 삭제됨 (미사용)</v>
-      </c>
       <c r="G16" t="str">
         <v>X</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B17" t="str">
         <v>GI_REQ_DATE</v>
@@ -775,10 +770,13 @@
       <c r="H17" t="str">
         <v>출하요청일은 실제 해당 상품이 출고가 되기로 한 예정일자 입니다. 직납의 경우가 아닌 대부분의 경우, 센터로 출고하는 날짜입니다.</v>
       </c>
+      <c r="I17" t="str">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B18" t="str">
         <v>BL_NO</v>
@@ -796,16 +794,19 @@
         <v>BL 스피너(sp_bl_no) 목록 구성, BL스캔 시 temp_bl_no와 비교하여 해당 상품 검색, 서버전송 패킷에 포함</v>
       </c>
       <c r="G18" t="str" xml:space="preserve">
-        <v xml:space="preserve">_x000d_
+        <v xml:space="preserve">_x000d__x000d_
 월품목별재고화일_LOT별_VIEW.BL_NO</v>
       </c>
       <c r="H18" t="str">
         <v xml:space="preserve">BL번호라고 되어 있지만, 실제로는 수입이력번호 입니다. 수입이력번호가 없을 때, BL번호를 참고적으로 넣은 것입니다. , 아주 드문 Case 로 수입이력번호가 없을 수 있습니다.  그 때만 BL번호를 입력해서 참고하도록 한 것입니다. </v>
       </c>
+      <c r="I18" t="str">
+        <v>BL2026030001</v>
+      </c>
     </row>
     <row r="19" xml:space="preserve">
       <c r="A19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B19" t="str">
         <v>BRAND_CODE</v>
@@ -819,20 +820,17 @@
       <c r="E19" t="str">
         <v>서버전송 (JSP 미사용)</v>
       </c>
-      <c r="F19" t="str">
-        <v>Goodswets_Info.setBRAND_CODE()로 저장, 서버전송 패킷 구성(GI_D_ID::ITEM_CODE::BRAND_CODE::REG_ID)</v>
-      </c>
       <c r="G19" t="str">
         <v>?</v>
       </c>
       <c r="H19" t="str" xml:space="preserve">
-        <v xml:space="preserve">사실상 이용하지 않는 정보입니다. ERP 상에서는 PACKER 품목코드 입력할 때, brand 코드를 입력합니다.  아래의 브랜드명은 이 브랜드코드를 명칭으로 전환한 것이고, 해당 코드와 브랜드의 정보는  공통코드 테이블에 정보가 있습니다. _x000d_
+        <v xml:space="preserve">사실상 이용하지 않는 정보입니다. ERP 상에서는 PACKER 품목코드 입력할 때, brand 코드를 입력합니다.  아래의 브랜드명은 이 브랜드코드를 명칭으로 전환한 것이고, 해당 코드와 브랜드의 정보는  공통코드 테이블에 정보가 있습니다. _x000d__x000d_
 Select * from b_common_code where mater_code = 'BRAND'   를 조회하면 나옵니다.</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>15</v>
+      <c r="A20" t="str">
+        <v>-</v>
       </c>
       <c r="B20" t="str">
         <v>BRANDNAME</v>
@@ -846,16 +844,13 @@
       <c r="E20" t="str">
         <v>미사용</v>
       </c>
-      <c r="F20" t="str">
-        <v>v28에서 로컬DB 삭제됨 (미사용)</v>
-      </c>
       <c r="G20" t="str">
         <v>X</v>
       </c>
     </row>
     <row r="21" xml:space="preserve">
       <c r="A21">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B21" t="str">
         <v>CLIENT_CODE</v>
@@ -876,20 +871,20 @@
         <v>SM_마트사발주이마트.점포코드</v>
       </c>
       <c r="H21" t="str" xml:space="preserve">
-        <v xml:space="preserve">해당 코드는  최종도착지(지점) 의 거래처 코드입니다.  출고할 때의 최종도착지의 코드이고, 어떤 지점으로 나가는지 알수 있는 코드입니다._x000d_
-데이터를 가져오는 방법은_x000d_
-발주서 테이블 W_Emart_order_item (이마트 발주서의 경우) 에 발주서 상의 "지점코드" 4자리로 최종도착지 지점의 거래처 코드를 맵핑합니다._x000d_
-_x000d_
-Select * from b_common_code where master_code = 'EMART_STORE_CODE '      _x000d_
+        <v xml:space="preserve">해당 코드는  최종도착지(지점) 의 거래처 코드입니다.  출고할 때의 최종도착지의 코드이고, 어떤 지점으로 나가는지 알수 있는 코드입니다._x000d__x000d_
+데이터를 가져오는 방법은_x000d__x000d_
+발주서 테이블 W_Emart_order_item (이마트 발주서의 경우) 에 발주서 상의 "지점코드" 4자리로 최종도착지 지점의 거래처 코드를 맵핑합니다._x000d__x000d_
+_x000d__x000d_
+Select * from b_common_code where master_code = 'EMART_STORE_CODE '      _x000d__x000d_
 위 쿼리를 조회하면 이마트가 말하는 지점코드와 ERP 상의 거래처코드가 맵핑되어 있는데, 위 테이블의 값을 통해서 어떤 발주서상의 지점코드만 가지고 ERP의 어떤 거래처코드와 맵핑되어 야 하는지 확인합니다. </v>
       </c>
-      <c r="I21">
-        <v>2006</v>
+      <c r="I21" t="str">
+        <v>CL001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B22" t="str">
         <v>CLIENTNAME</v>
@@ -913,12 +908,12 @@
         <v xml:space="preserve"> * 위 출고업체 코드에 해당하는 지점명 </v>
       </c>
       <c r="I22" t="str">
-        <v>E/T안산점</v>
+        <v>이마트 이천센터</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B23" t="str">
         <v>CENTERNAME</v>
@@ -942,12 +937,12 @@
         <v>W_Emart_order_item.Center_code 컬럼의 값을 Select * from b_common_code where master_code = 'EMART_STORE_CODE '      에 매칭시켜서, 센터명을 가져옵니다.</v>
       </c>
       <c r="I23" t="str">
-        <v>이마트센터코드</v>
+        <v>이마트 이천센터</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B24" t="str">
         <v>ITEM_SPEC</v>
@@ -967,10 +962,13 @@
       <c r="G24" t="str">
         <v>CO_품목코드.규격</v>
       </c>
+      <c r="I24" t="str">
+        <v>척아이롤/냉장</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B25" t="str">
         <v>CT_CODE</v>
@@ -990,10 +988,13 @@
       <c r="G25" t="str">
         <v>CO_품목코드.원산지</v>
       </c>
+      <c r="I25" t="str">
+        <v>AU</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B26" t="str">
         <v>PACKER_CODE</v>
@@ -1014,12 +1015,12 @@
         <v>CO_품목코드.가공장코드</v>
       </c>
       <c r="I26">
-        <v>111</v>
+        <v>30228</v>
       </c>
     </row>
     <row r="27" xml:space="preserve">
       <c r="A27">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B27" t="str">
         <v>IMPORT_ID_NO</v>
@@ -1037,13 +1038,16 @@
         <v>UI 스피너에 BL_NO와 함께 표시, 바코드 생성 시 수입이력번호 부분으로 사용, LabelPrintHelper SLCS 라벨에 수입식별번호 출력</v>
       </c>
       <c r="G27" t="str" xml:space="preserve">
-        <v xml:space="preserve">월품목별재고화일_LOT별_VIEW.이력번호_x000d_
+        <v xml:space="preserve">월품목별재고화일_LOT별_VIEW.이력번호_x000d__x000d_
 </v>
       </c>
+      <c r="I27" t="str">
+        <v>123456789012</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>23</v>
+      <c r="A28" t="str">
+        <v>-</v>
       </c>
       <c r="B28" t="str">
         <v>PACKERNAME</v>
@@ -1057,16 +1061,13 @@
       <c r="E28" t="str">
         <v>미사용</v>
       </c>
-      <c r="F28" t="str">
-        <v>v28에서 로컬DB 삭제됨 (미사용)</v>
-      </c>
       <c r="G28" t="str">
         <v>X</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B29" t="str">
         <v>PACKER_PRODUCT_CODE</v>
@@ -1086,10 +1087,13 @@
       <c r="G29" t="str">
         <v>CO_품목코드.PPCODE</v>
       </c>
+      <c r="I29" t="str">
+        <v>20001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B30" t="str">
         <v>BARCODE_TYPE</v>
@@ -1115,7 +1119,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B31" t="str">
         <v>ITEM_TYPE</v>
@@ -1135,10 +1139,13 @@
       <c r="G31" t="str">
         <v>추가필요</v>
       </c>
+      <c r="I31" t="str">
+        <v>W</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B32" t="str">
         <v>PACKWEIGHT</v>
@@ -1158,10 +1165,13 @@
       <c r="G32" t="str">
         <v>CO_품목코드.박스중량</v>
       </c>
+      <c r="I32" t="str">
+        <v>5.67</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B33" t="str">
         <v>BARCODEGOODS</v>
@@ -1181,10 +1191,13 @@
       <c r="G33" t="str">
         <v>CO_품목코드.상품바코드</v>
       </c>
+      <c r="I33" t="str">
+        <v>20001</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B34" t="str">
         <v>STORE_IN_DATE</v>
@@ -1207,10 +1220,13 @@
       <c r="H34" t="str">
         <v>지점에 출고하는 날짜 - 매출일자로 처리되어야 합니다.</v>
       </c>
+      <c r="I34" t="str">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>30</v>
+      <c r="A35" t="str">
+        <v>-</v>
       </c>
       <c r="B35" t="str">
         <v>GR_WAREHOUSE_CODE</v>
@@ -1233,10 +1249,13 @@
       <c r="H35" t="str">
         <v>PDA에서 어느 창고에 있는 재고를 출고하는지 선택해야하기 때문에, 사용하는 정보입니다.</v>
       </c>
+      <c r="I35" t="str">
+        <v>WH01</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B36" t="str">
         <v>EMARTLOGIS_CODE</v>
@@ -1256,10 +1275,13 @@
       <c r="G36" t="str">
         <v>CO_매출처품목코드매핑.바코드타입</v>
       </c>
+      <c r="I36" t="str">
+        <v>0000000</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>32</v>
+      <c r="A37" t="str">
+        <v>-</v>
       </c>
       <c r="B37" t="str">
         <v>EMARTLOGIS_NAME</v>
@@ -1273,16 +1295,13 @@
       <c r="E37" t="str">
         <v>미사용</v>
       </c>
-      <c r="F37" t="str">
-        <v>v28에서 로컬DB 삭제됨 (미사용)</v>
-      </c>
       <c r="G37" t="str">
         <v>X</v>
       </c>
     </row>
     <row r="38" xml:space="preserve">
       <c r="A38">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B38" t="str">
         <v>WH_AREA</v>
@@ -1300,17 +1319,20 @@
         <v>LabelPrintHelper SLCS 라벨에 창고구역 출력(위치 385,305 / 폰트 65x65)</v>
       </c>
       <c r="G38" t="str" xml:space="preserve">
-        <v xml:space="preserve">컬럼추가_x000d_
-_x000d_
+        <v xml:space="preserve">컬럼추가_x000d__x000d_
+_x000d__x000d_
 이마트 센터의 경우 창고구역 입력 가능</v>
       </c>
       <c r="H38" t="str">
         <v>이마트 출고에 대한 경우이고, Select  *  from b_common_code where master_code = 'EMART_STORE_CODE '    정보에,  REF_CODE2 컬럼이 창고구역  정보가 입력된 컬럼이고, 필요시 이 차제를 그대로 출력해주면 됩니다.  값이 없는 지점도 있기 때문에, null 값이 허용되어야 합니다.</v>
       </c>
+      <c r="I38" t="str">
+        <v>A1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B39" t="str">
         <v>USE_NAME</v>
@@ -1330,10 +1352,13 @@
       <c r="G39" t="str">
         <v>CO_품목코드.제품용도</v>
       </c>
+      <c r="I39" t="str">
+        <v>원료육</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B40" t="str">
         <v>USE_CODE</v>
@@ -1350,10 +1375,13 @@
       <c r="F40" t="str">
         <v>특정 BARCODE_TYPE에서 바코드 생성 시 포함(상품코드+수입이력번호+용도코드)</v>
       </c>
+      <c r="I40" t="str">
+        <v>01</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B41" t="str">
         <v>CT_NAME</v>
@@ -1373,10 +1401,13 @@
       <c r="G41" t="str">
         <v>CO_품목코드.원산지</v>
       </c>
+      <c r="I41" t="str">
+        <v>호주산</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B42" t="str">
         <v>STORE_CODE</v>
@@ -1396,10 +1427,13 @@
       <c r="G42" t="str">
         <v>SM_마트사이마트.점포코드</v>
       </c>
+      <c r="I42" t="str">
+        <v>1234 (미트센터: 9231)</v>
+      </c>
     </row>
     <row r="43" xml:space="preserve">
       <c r="A43">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B43" t="str">
         <v>EMART_PLANT_CODE</v>
@@ -1420,14 +1454,14 @@
         <v>?</v>
       </c>
       <c r="H43" t="str" xml:space="preserve">
-        <v xml:space="preserve">이마트 미트센터 납품시, 이마트 요청에 의해서 공장코드를 라벨에 출력할 경우가 있기 때문에 해당정보를 관리했었습니다.  해당 정보는 품목정보의 추가정보 입력으로 관리되며, 들어가야 할 내용은 이마트가 특정해서 코드값을 정해줍니다. _x000d_
-_x000d_
+        <v xml:space="preserve">이마트 미트센터 납품시, 이마트 요청에 의해서 공장코드를 라벨에 출력할 경우가 있기 때문에 해당정보를 관리했었습니다.  해당 정보는 품목정보의 추가정보 입력으로 관리되며, 들어가야 할 내용은 이마트가 특정해서 코드값을 정해줍니다. _x000d__x000d_
+_x000d__x000d_
 최근 몇년동안 해당 컬럼을 사용하지 않았고,  수년전에, 단 한번 사용되었습니다.</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>39</v>
+      <c r="A44" t="str">
+        <v>-</v>
       </c>
       <c r="B44" t="str">
         <v>MAJOR_CATEGORY</v>
@@ -1441,16 +1475,13 @@
       <c r="E44" t="str">
         <v>앱미전달</v>
       </c>
-      <c r="F44" t="str">
-        <v>DB에 저장만 되고 앱에서 직접 사용하지 않음</v>
-      </c>
       <c r="G44" t="str">
         <v>X</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>40</v>
+      <c r="A45" t="str">
+        <v>-</v>
       </c>
       <c r="B45" t="str">
         <v>CONTAINER_TYPE</v>
@@ -1463,9 +1494,6 @@
       </c>
       <c r="E45" t="str">
         <v>앱미전달</v>
-      </c>
-      <c r="F45" t="str">
-        <v>DB에 저장만 되고 앱에서 직접 사용하지 않음</v>
       </c>
       <c r="G45" t="str">
         <v>X</v>
@@ -1478,45 +1506,1667 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>1. CLIENT_CODE, STORE_CODE 두 컬럼 다 지점을 나타내는 것이 맞나요?</v>
+        <v>0. 어떻게 사용하는지 정리한 글에 대해 한 번 확인 부탁드립니다</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2. EMART_PLANT_CODE 해당 컬럼 삭제를 해도 되나요</v>
+        <v>1. CLIENT_CODE, STORE_CODE 두 컬럼 다 지점을 나타내는 것이 맞나요?</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>3. VW_PDA_WID_LIST 해당 VIEW의 경우 ITEM_TYPE 'W'만 조회하는것이 맞나요?</v>
+        <v>2. EMART_PLANT_CODE 해당 컬럼 삭제를 해도 되나요</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>4. PACKER_CODE가 가공장 코드가 맞나요?</v>
+        <v>3. VW_PDA_WID_LIST 해당 VIEW의 경우 ITEM_TYPE 'W'만 조회하는것이 맞는지, ITEM_TYPE의 각 항목의 정의가 맞는지?</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>4. 하나의 품목에서 ITEM_TYPE이 여러 개 일 수 있나요?</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>5. PACKER_CODE가 가공장 코드가 맞나요?</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A61:G61"/>
     <mergeCell ref="A56:G56"/>
     <mergeCell ref="A57:G57"/>
     <mergeCell ref="A58:G58"/>
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I61"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I30"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>미사용 컬럼</v>
+      </c>
+      <c r="C1" t="str">
+        <v>컬럼추가</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>질문 컬럼</v>
+      </c>
+      <c r="C2" t="str">
+        <v>G3 어디서 입력하는지, 데이터를 어떻게 관리하는지</v>
+      </c>
+      <c r="I2" t="str">
+        <v>품목코드 : 1210300001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>VW_PDA_WID_HOMEPLUS_LIST</v>
+      </c>
+      <c r="I3" t="str">
+        <v>품목명 : 호주산 척아이롤</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Index</v>
+      </c>
+      <c r="B4" t="str">
+        <v>컬럼명</v>
+      </c>
+      <c r="C4" t="str">
+        <v>데이터 출처</v>
+      </c>
+      <c r="D4" t="str">
+        <v>설명</v>
+      </c>
+      <c r="E4" t="str">
+        <v>용도</v>
+      </c>
+      <c r="F4" t="str">
+        <v>어떻게 사용되는지</v>
+      </c>
+      <c r="G4" t="str">
+        <v>여부</v>
+      </c>
+      <c r="H4" t="str">
+        <v>중요 답변</v>
+      </c>
+      <c r="I4" t="str">
+        <v>샘플 데이터</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="str">
+        <v>GI_D_ID</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ID.GI_D_ID</v>
+      </c>
+      <c r="D5" t="str">
+        <v>출고상세ID (PK)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>서버전송(PK)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>wet_data_insert()에서 Goodswets_Info.setGI_D_ID()로 저장, 서버전송 패킷 구성(GI_D_ID::ITEM_CODE::BRAND_CODE::REG_ID), DBHandler.duplicatequeryGoodsWet() WHERE 조건</v>
+      </c>
+      <c r="G5" t="str">
+        <v>SM_출고상세.SEQ</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ITEM_CODE</v>
+      </c>
+      <c r="C6" t="str">
+        <v>ID.ITEM_CODE</v>
+      </c>
+      <c r="D6" t="str">
+        <v>상품코드</v>
+      </c>
+      <c r="E6" t="str">
+        <v>서버전송</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Goodswets_Info.setITEM_CODE()로 저장, 서버전송 패킷 구성에 포함</v>
+      </c>
+      <c r="G6" t="str">
+        <v>CO_품목코드.제품코드</v>
+      </c>
+      <c r="I6">
+        <v>1210300001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ITEM_NAME</v>
+      </c>
+      <c r="C7" t="str">
+        <v>[해외매입] DECODE(EO.ITEM_NAME, NULL, DE_ITEM(ID.ITEM_CODE), EO.ITEM_NAME) / [국내매입] DE_ITEM(ID.ITEM_CODE)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>상품명</v>
+      </c>
+      <c r="E7" t="str">
+        <v>화면표시</v>
+      </c>
+      <c r="F7" t="str">
+        <v>edit_product_name.setText()로 UI 표시, ShipmentListAdapter에서 리스트 항목 표시</v>
+      </c>
+      <c r="G7" t="str">
+        <v>CO_품목코드.제품명</v>
+      </c>
+      <c r="I7" t="str">
+        <v>호주산 척아이롤</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>EMARTITEM_CODE</v>
+      </c>
+      <c r="C8" t="str">
+        <v>EO.ITEM_CODE (W_E_ORDER_ITEM)</v>
+      </c>
+      <c r="D8" t="str">
+        <v>홈플러스 발주서 상품코드</v>
+      </c>
+      <c r="E8" t="str">
+        <v>미사용(저장만)</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Goodswets_Info.setEMARTITEM_CODE()로 저장은 되나 홈플러스 라벨(setHomeplusPrinting)에 미출력, insert_goods_wet_homeplus.jsp 서버 패킷에도 미포함</v>
+      </c>
+      <c r="G8" t="str">
+        <v>CO_매출처품목코드매핑.거래처제품코드</v>
+      </c>
+      <c r="I8" t="str">
+        <v>HP2800010000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>EMARTITEM</v>
+      </c>
+      <c r="C9" t="str">
+        <v>EO.ITEM_NAME (W_E_ORDER_ITEM)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>홈플러스 발주서 상품명</v>
+      </c>
+      <c r="E9" t="str">
+        <v>라벨출력</v>
+      </c>
+      <c r="F9" t="str">
+        <v>setHomeplusPrinting()에서 SLCS 명령으로 라벨 상품명([3]위치) 출력, 17자 초과 시 폰트 25, 이하 시 폰트 30</v>
+      </c>
+      <c r="G9" t="str">
+        <v>CO_매출처품목코드매핑.거래처제품명</v>
+      </c>
+      <c r="I9" t="str">
+        <v>호주산 척아이롤(냉장)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>GI_REQ_PKG</v>
+      </c>
+      <c r="C10" t="str">
+        <v>ID.GI_REQ_PKG</v>
+      </c>
+      <c r="D10" t="str">
+        <v>출하요청수량</v>
+      </c>
+      <c r="E10" t="str">
+        <v>화면표시, 로직분기</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PACKING_QTY와 비교하여 계근 완료 판단, edit_wet_count UI 표시, centerTotalCount 합산</v>
+      </c>
+      <c r="G10" t="str">
+        <v>SM_출고상세.출고수량</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="str">
+        <v>GI_REQ_QTY</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ID.GI_REQ_QTY</v>
+      </c>
+      <c r="D11" t="str">
+        <v>출하요청중량</v>
+      </c>
+      <c r="E11" t="str">
+        <v>화면표시(진행률)</v>
+      </c>
+      <c r="F11" t="str">
+        <v>edit_wet_weight UI에 요청중량 표시, centerTotalWeight 합산 계산</v>
+      </c>
+      <c r="G11" t="str">
+        <v>SM_출고상세.출고중량</v>
+      </c>
+      <c r="I11" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" t="str">
+        <v>GI_REQ_DATE</v>
+      </c>
+      <c r="C12" t="str">
+        <v>GI_REQ_DATE</v>
+      </c>
+      <c r="D12" t="str">
+        <v>출하요청일</v>
+      </c>
+      <c r="E12" t="str">
+        <v>앱전달, 앱내미사용(JSP WHERE: GI_REQ_DATE = Common.selectDay)</v>
+      </c>
+      <c r="F12" t="str">
+        <v>JSP WHERE절에서 GI_REQ_DATE = Common.selectDay(앱에서 선택한 날짜) 조건으로 필터링. VIEW 자체 WHERE절에도 IH.GI_REQ_DATE &gt;= SYSDATE 조건 있음. 컬럼값은 앱에 전달되나 앱 내 화면/로직에 미사용</v>
+      </c>
+      <c r="G12" t="str">
+        <v>SM_출고상세.출고일자</v>
+      </c>
+      <c r="I12" t="str">
+        <v>20260310</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>8</v>
+      </c>
+      <c r="B13" t="str">
+        <v>BL_NO</v>
+      </c>
+      <c r="C13" t="str">
+        <v>DECODE(WR.IMPORT_ID_NO, NULL, WR.BL_NO, WR.IMPORT_ID_NO)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>BL번호(수입이력번호 우선)</v>
+      </c>
+      <c r="E13" t="str">
+        <v>화면표시, 중복스캔방지</v>
+      </c>
+      <c r="F13" t="str">
+        <v>BL 스피너(sp_bl_no) 목록 구성, BL스캔 시 temp_bl_no와 비교하여 해당 상품 검색, 서버전송 패킷에 포함</v>
+      </c>
+      <c r="G13" t="str">
+        <v>월품목별재고화일_LOT별_VIEW.BL_NO</v>
+      </c>
+      <c r="H13" t="str">
+        <v>수입이력번호가 있으면 수입이력번호, 없으면 BL번호를 반환</v>
+      </c>
+      <c r="I13" t="str">
+        <v>BL2026030001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>9</v>
+      </c>
+      <c r="B14" t="str">
+        <v>BRAND_CODE</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ID.BRAND_CODE</v>
+      </c>
+      <c r="D14" t="str">
+        <v>브랜드코드</v>
+      </c>
+      <c r="E14" t="str">
+        <v>서버전송</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Goodswets_Info.setBRAND_CODE()로 저장, 서버전송 패킷 구성에 포함</v>
+      </c>
+      <c r="G14" t="str">
+        <v>?</v>
+      </c>
+      <c r="I14" t="str">
+        <v>BR01</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15" t="str">
+        <v>CLIENT_CODE</v>
+      </c>
+      <c r="C15" t="str">
+        <v>IH.CLIENT_CODE</v>
+      </c>
+      <c r="D15" t="str">
+        <v>출고업체코드</v>
+      </c>
+      <c r="E15" t="str">
+        <v>로직분기(DB조회조건)</v>
+      </c>
+      <c r="F15" t="str">
+        <v>DBHandler 조회 시 WHERE 조건으로 사용, Goodswets_Info에 저장</v>
+      </c>
+      <c r="G15" t="str">
+        <v>SM_출고머리.CLIENT_CODE (W_GOODS_IH.CLIENT_CODE)</v>
+      </c>
+      <c r="H15" t="str">
+        <v>홈플러스 발주서의 최종도착지(지점) 거래처 코드</v>
+      </c>
+      <c r="I15" t="str">
+        <v>CL001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>11</v>
+      </c>
+      <c r="B16" t="str">
+        <v>CLIENTNAME</v>
+      </c>
+      <c r="C16" t="str">
+        <v>DECODE(SUBSTR(EO.CENTERNAME,1,2),'CJ',DE_CLIENT2(IH.CLIENT_CODE)||'('||EO.STORECODE||')',EO.STORENAME)</v>
+      </c>
+      <c r="D16" t="str">
+        <v>출고업체명(지점명)</v>
+      </c>
+      <c r="E16" t="str">
+        <v>화면표시, 라벨출력</v>
+      </c>
+      <c r="F16" t="str">
+        <v>setHomeplusPrinting()에서 pointName으로 저장, 라벨 [1]지점명 출력 (6자 초과 시 폰트 70, 이하 시 폰트 100)</v>
+      </c>
+      <c r="G16" t="str">
+        <v>W_E_ORDER_ITEM.STORE_NAME (CJ인 경우 DE_CLIENT2 함수)</v>
+      </c>
+      <c r="H16" t="str">
+        <v>CJ물류센터이면 DE_CLIENT2(거래처명)+점포코드, 그 외에는 STORENAME(W_E_ORDER_ITEM.STORE_NAME)</v>
+      </c>
+      <c r="I16" t="str">
+        <v>홈플러스 안산점</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17" t="str">
+        <v>CENTERNAME</v>
+      </c>
+      <c r="C17" t="str">
+        <v>B_COMMON_CODE (MASTER_CODE=HOMEPLUS_STORE_CODE).CODE_NAME</v>
+      </c>
+      <c r="D17" t="str">
+        <v>홈플러스 센터명</v>
+      </c>
+      <c r="E17" t="str">
+        <v>로직분기</v>
+      </c>
+      <c r="F17" t="str">
+        <v>B_COMMON_CODE.HOMEPLUS_STORE_CODE 기준으로 조회, CLIENTNAME 도출 시 CJ 여부 판단에 사용</v>
+      </c>
+      <c r="G17" t="str">
+        <v>B_COMMON_CODE.CODE_NAME (HOMEPLUS_STORE_CODE)</v>
+      </c>
+      <c r="I17" t="str">
+        <v>홈플러스 경기물류센터</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ITEM_SPEC</v>
+      </c>
+      <c r="C18" t="str">
+        <v>WR.ITEM_SPEC</v>
+      </c>
+      <c r="D18" t="str">
+        <v>상품규격</v>
+      </c>
+      <c r="E18" t="str">
+        <v>미사용(저장만)</v>
+      </c>
+      <c r="F18" t="str">
+        <v>setHomeplusPrinting()에서 미사용. Goodswets_Info에 저장은 되나 홈플러스 라벨에 출력하지 않음</v>
+      </c>
+      <c r="G18" t="str">
+        <v>CO_품목코드.규격</v>
+      </c>
+      <c r="I18" t="str">
+        <v>척아이롤/냉장</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" t="str">
+        <v>CT_CODE</v>
+      </c>
+      <c r="C19" t="str">
+        <v>[해외매입] SELECT CT_NAME FROM B_COUNTRY WHERE CT_CODE=WR.CT_CODE / [국내매입] WR.CT_CODE</v>
+      </c>
+      <c r="D19" t="str">
+        <v>원산지 (해외매입은 CT_NAME, 국내매입은 CT_CODE)</v>
+      </c>
+      <c r="E19" t="str">
+        <v>라벨출력</v>
+      </c>
+      <c r="F19" t="str">
+        <v>setHomeplusPrinting()에서 라벨 [5]CT코드 출력. 주의: 해외매입 UNION은 CT_NAME(원산지명)이, 국내매입 UNION은 CT_CODE(원산지코드)가 들어옴</v>
+      </c>
+      <c r="G19" t="str">
+        <v>CO_품목코드.원산지</v>
+      </c>
+      <c r="H19" t="str">
+        <v>해외매입과 국내매입에서 데이터 형태가 다름 (명칭 vs 코드)</v>
+      </c>
+      <c r="I19" t="str">
+        <v>호주산 (해외) / AU (국내)</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20" t="str">
+        <v>IMPORT_ID_NO</v>
+      </c>
+      <c r="C20" t="str">
+        <v>NVL(WR.IMPORT_ID_NO, '            ')</v>
+      </c>
+      <c r="D20" t="str">
+        <v>수입식별번호 (null 방지)</v>
+      </c>
+      <c r="E20" t="str">
+        <v>화면표시, 라벨출력</v>
+      </c>
+      <c r="F20" t="str">
+        <v>setHomeplusPrinting()에서 라벨 [6] 수입식별번호 뒤 4자리(substring(8,12)) 출력, null 방지를 위해 NVL로 공백12자리 처리</v>
+      </c>
+      <c r="G20" t="str">
+        <v>월품목별재고화일_LOT별_VIEW.이력번호</v>
+      </c>
+      <c r="I20" t="str">
+        <v>123456789012</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21" t="str">
+        <v>PACKER_CODE</v>
+      </c>
+      <c r="C21" t="str">
+        <v>[해외매입] BD.PACKER_CODE (I_BL_D) / [국내매입] OD.PACKER_CODE (I_OFFER_D)</v>
+      </c>
+      <c r="D21" t="str">
+        <v>패커코드</v>
+      </c>
+      <c r="E21" t="str">
+        <v>로직분기(킬코이30228)</v>
+      </c>
+      <c r="F21" t="str">
+        <v>KILKOY_PACKER_CODE("30228")와 비교하여 킬코이 제품 판별 로직 분기</v>
+      </c>
+      <c r="G21" t="str">
+        <v>CO_품목코드.가공장코드</v>
+      </c>
+      <c r="I21">
+        <v>30228</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>17</v>
+      </c>
+      <c r="B22" t="str">
+        <v>PACKER_PRODUCT_CODE</v>
+      </c>
+      <c r="C22" t="str">
+        <v>[해외매입] BD.PACKER_PRODUCT_CODE / [국내매입] DECODE(OD.PACKER_PRODUCT_CODE, NULL, ID.ITEM_CODE, OD.PACKER_PRODUCT_CODE)</v>
+      </c>
+      <c r="D22" t="str">
+        <v>패커상품코드</v>
+      </c>
+      <c r="E22" t="str">
+        <v>화면표시, 서버전송</v>
+      </c>
+      <c r="F22" t="str">
+        <v>edit_product_code UI 표시, find_PackerProduct()에서 상품 검색 기준, duplicatequeryGoodsWet() WHERE 조건, 서버전송 시 사용</v>
+      </c>
+      <c r="G22" t="str">
+        <v>CO_품목코드.PPCODE</v>
+      </c>
+      <c r="I22" t="str">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="B23" t="str">
+        <v>BARCODE_TYPE</v>
+      </c>
+      <c r="C23" t="str">
+        <v>B_EMART_BARCODE.BARCODE_TYPE (ITEM_TYPE=W 조건 조회)</v>
+      </c>
+      <c r="D23" t="str">
+        <v>바코드타입</v>
+      </c>
+      <c r="E23" t="str">
+        <v>미사용(저장만)</v>
+      </c>
+      <c r="F23" t="str">
+        <v>setHomeplusPrinting()에서 미사용. setBarcodeMsg() 바코드파싱에도 미사용. 이마트 setPrinting()에서만 BARCODE_TYPE 분기 사용. searchType=2/5는 BARCODE_TYPE 무관하게 setHomeplusPrinting() 고정 호출</v>
+      </c>
+      <c r="G23" t="str">
+        <v>CO_매출처품목코드매핑.바코드타입</v>
+      </c>
+      <c r="I23" t="str">
+        <v>M0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>19</v>
+      </c>
+      <c r="B24" t="str">
+        <v>ITEM_TYPE</v>
+      </c>
+      <c r="C24" t="str">
+        <v>S 하드코딩 (VIEW에서 고정)</v>
+      </c>
+      <c r="D24" t="str">
+        <v>아이템타입</v>
+      </c>
+      <c r="E24" t="str">
+        <v>로직분기(계근방식)</v>
+      </c>
+      <c r="F24" t="str">
+        <v>항상 S(저울계근) 고정. setHomeplusPrinting()에서 ITEM_TYPE=B(비정량) 분기가 있으나 이 VIEW에서는 항상 S이므로 B 분기 미진입</v>
+      </c>
+      <c r="G24" t="str">
+        <v>고정값</v>
+      </c>
+      <c r="H24" t="str">
+        <v>홈플러스 VIEW에서 S로 하드코딩. B_EMART_BARCODE.ITEM_TYPE=W로 JOIN하면서 실제 ITEM_TYPE은 무시</v>
+      </c>
+      <c r="I24" t="str">
+        <v>S</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>20</v>
+      </c>
+      <c r="B25" t="str">
+        <v>PACKWEIGHT</v>
+      </c>
+      <c r="C25" t="str">
+        <v>B_EMART_BARCODE.PACKWEIGHT</v>
+      </c>
+      <c r="D25" t="str">
+        <v>포장중량</v>
+      </c>
+      <c r="E25" t="str">
+        <v>미사용(저장만)</v>
+      </c>
+      <c r="F25" t="str">
+        <v>ITEM_TYPE=J(제품계근) 시 사용하나, 홈플러스 VIEW는 ITEM_TYPE=S 고정이므로 J타입 계근 미발생. Goodswets_Info에 저장만 됨</v>
+      </c>
+      <c r="G25" t="str">
+        <v>CO_품목코드.박스중량</v>
+      </c>
+      <c r="I25" t="str">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>21</v>
+      </c>
+      <c r="B26" t="str">
+        <v>BARCODEGOODS</v>
+      </c>
+      <c r="C26" t="str">
+        <v>[해외매입] SELECT BARCODEGOODS FROM S_BARCODE_INFO WHERE PACKER_CLIENT_CODE=BD.PACKER_CODE AND PACKER_PRODUCT_CODE=BD.PACKER_PRODUCT_CODE AND STATUS=Y / [국내매입] DECODE(OD.PACKER_PRODUCT_CODE, NULL, ID.ITEM_CODE, SELECT FROM S_BARCODE_INFO)</v>
+      </c>
+      <c r="D26" t="str">
+        <v>바코드상품코드</v>
+      </c>
+      <c r="E26" t="str">
+        <v>아이템검색</v>
+      </c>
+      <c r="F26" t="str">
+        <v>find_PackerProductBarcodeGoods()에서 스캔 바코드와 비교하여 상품 매칭, work_item_barcodegoods에 저장</v>
+      </c>
+      <c r="G26" t="str">
+        <v>CO_품목코드.상품바코드</v>
+      </c>
+      <c r="I26" t="str">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>22</v>
+      </c>
+      <c r="B27" t="str">
+        <v>STORE_IN_DATE</v>
+      </c>
+      <c r="C27" t="str">
+        <v>W_E_ORDER_ITEM.STORE_IN_DATE</v>
+      </c>
+      <c r="D27" t="str">
+        <v>입고일자(납품일자)</v>
+      </c>
+      <c r="E27" t="str">
+        <v>라벨출력</v>
+      </c>
+      <c r="F27" t="str">
+        <v>setHomeplusPrinting()에서 라벨 [7]납품일자 출력 (YYYY년 MM월 DD일 포맷)</v>
+      </c>
+      <c r="G27" t="str">
+        <v>SM_수주상세.납기일자</v>
+      </c>
+      <c r="I27" t="str">
+        <v>20260310</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>23</v>
+      </c>
+      <c r="B28" t="str">
+        <v>EMARTLOGIS_CODE</v>
+      </c>
+      <c r="C28" t="str">
+        <v>EO.STORECODE (W_E_ORDER_ITEM.STORE_CODE)</v>
+      </c>
+      <c r="D28" t="str">
+        <v>홈플러스 점포코드</v>
+      </c>
+      <c r="E28" t="str">
+        <v>라벨출력, 로직분기</v>
+      </c>
+      <c r="F28" t="str">
+        <v>setHomeplusPrinting()에서 pointCode로 저장, ITEM_TYPE!=B이면 라벨 [2]지점코드 출력. 홈플러스에서는 STORECODE를 EMARTLOGIS_CODE로 사용</v>
+      </c>
+      <c r="G28" t="str">
+        <v>W_E_ORDER_ITEM.STORE_CODE</v>
+      </c>
+      <c r="H28" t="str">
+        <v>EMARTLOGIS_CODE와 HOMPLUS_STORE_CODE 모두 동일한 EO.STORECODE에서 파생</v>
+      </c>
+      <c r="I28" t="str">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>-</v>
+      </c>
+      <c r="B29" t="str">
+        <v>GR_WAREHOUSE_CODE</v>
+      </c>
+      <c r="C29" t="str">
+        <v>WR.GR_WAREHOUSE_CODE</v>
+      </c>
+      <c r="D29" t="str">
+        <v>창고코드</v>
+      </c>
+      <c r="E29" t="str">
+        <v>JSP미전달(WHERE조건용)</v>
+      </c>
+      <c r="F29" t="str">
+        <v>VIEW에 존재하나 JSP SELECT에 미포함, 앱으로 전달 안 됨</v>
+      </c>
+      <c r="G29" t="str">
+        <v>SM_출고상세.창고코드</v>
+      </c>
+      <c r="I29" t="str">
+        <v>WH01</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>-</v>
+      </c>
+      <c r="B30" t="str">
+        <v>HOMPLUS_STORE_CODE</v>
+      </c>
+      <c r="C30" t="str">
+        <v>EO.STORECODE (W_E_ORDER_ITEM.STORE_CODE)</v>
+      </c>
+      <c r="D30" t="str">
+        <v>홈플러스 점포코드(정렬용)</v>
+      </c>
+      <c r="E30" t="str">
+        <v>JSP미전달(ORDER BY만 사용)</v>
+      </c>
+      <c r="F30" t="str">
+        <v>VIEW에 존재하나 JSP SELECT에 미포함, search_shipment_homeplus.jsp의 ORDER BY HOMPLUS_STORE_CODE ASC 정렬 기준으로만 사용</v>
+      </c>
+      <c r="G30" t="str">
+        <v>W_E_ORDER_ITEM.STORE_CODE</v>
+      </c>
+      <c r="H30" t="str">
+        <v>EMARTLOGIS_CODE와 동일값, Java에 전달 안 됨</v>
+      </c>
+      <c r="I30" t="str">
+        <v>1234</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I30"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I31"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>미사용 컬럼</v>
+      </c>
+      <c r="C1" t="str">
+        <v>컬럼추가</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>질문 컬럼</v>
+      </c>
+      <c r="C2" t="str">
+        <v>G3 어디서 입력하는지, 데이터를 어떻게 관리하는지</v>
+      </c>
+      <c r="I2" t="str">
+        <v>품목코드 : 1210300001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="I3" t="str">
+        <v>품목명 : 호주산 척아이롤</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Index</v>
+      </c>
+      <c r="B4" t="str">
+        <v>컬럼명</v>
+      </c>
+      <c r="C4" t="str">
+        <v>데이터 출처</v>
+      </c>
+      <c r="D4" t="str">
+        <v>설명</v>
+      </c>
+      <c r="E4" t="str">
+        <v>용도</v>
+      </c>
+      <c r="F4" t="str">
+        <v>어떻게 사용되는지</v>
+      </c>
+      <c r="G4" t="str">
+        <v>여부</v>
+      </c>
+      <c r="H4" t="str">
+        <v>중요 답변</v>
+      </c>
+      <c r="I4" t="str">
+        <v>샘플 데이터</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="str">
+        <v>GI_D_ID</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ID.GI_D_ID</v>
+      </c>
+      <c r="D5" t="str">
+        <v>출고상세ID (PK)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>서버전송(PK)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>wet_data_insert()에서 Goodswets_Info.setGI_D_ID()로 저장, 서버전송 패킷 구성</v>
+      </c>
+      <c r="G5" t="str">
+        <v>SM_출고상세.SEQ</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ITEM_CODE</v>
+      </c>
+      <c r="C6" t="str">
+        <v>ID.ITEM_CODE</v>
+      </c>
+      <c r="D6" t="str">
+        <v>상품코드</v>
+      </c>
+      <c r="E6" t="str">
+        <v>서버전송</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Goodswets_Info.setITEM_CODE()로 저장, 서버전송 패킷 포함</v>
+      </c>
+      <c r="G6" t="str">
+        <v>CO_품목코드.제품코드</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>1210300001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ITEM_NAME</v>
+      </c>
+      <c r="C7" t="str">
+        <v>DE_ITEM(ID.ITEM_CODE)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>상품명</v>
+      </c>
+      <c r="E7" t="str">
+        <v>화면표시</v>
+      </c>
+      <c r="F7" t="str">
+        <v>edit_product_name.setText()로 UI 표시, ShipmentListAdapter 리스트 표시</v>
+      </c>
+      <c r="G7" t="str">
+        <v>CO_품목코드.제품명</v>
+      </c>
+      <c r="H7" t="str">
+        <v>이마트와 달리 UNION 양쪽 모두 항상 DE_ITEM() 함수 사용</v>
+      </c>
+      <c r="I7" t="str">
+        <v>호주산 척아이롤</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>EMARTITEM_CODE</v>
+      </c>
+      <c r="C8" t="str">
+        <v>wmoi.MART_ITEMCODE (W_MART_ORDER_ITEM)</v>
+      </c>
+      <c r="D8" t="str">
+        <v>롯데마트 발주서 상품코드</v>
+      </c>
+      <c r="E8" t="str">
+        <v>라벨바코드</v>
+      </c>
+      <c r="F8" t="str">
+        <v>setPrintingLotte()에서 L0 중량바코드 앞 6자리(substring(0,6)) 생성에 사용 (LabelPrintHelper:1301)</v>
+      </c>
+      <c r="G8" t="str">
+        <v>CO_매출처품목코드매핑.거래처제품코드</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>L012345678</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>EMARTITEM</v>
+      </c>
+      <c r="C9" t="str">
+        <v>wmoi.MART_ITEMNAME (W_MART_ORDER_ITEM)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>롯데마트 발주서 상품명</v>
+      </c>
+      <c r="E9" t="str">
+        <v>라벨출력</v>
+      </c>
+      <c r="F9" t="str">
+        <v>setPrintingLotte()에서 라벨 [1]상품명 출력 (si.EMARTITEM, LabelPrintHelper:1356)</v>
+      </c>
+      <c r="G9" t="str">
+        <v>CO_매출처품목코드매핑.거래처제품명</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>호주산 척아이롤(냉장)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>GI_REQ_PKG</v>
+      </c>
+      <c r="C10" t="str">
+        <v>ID.GI_REQ_PKG</v>
+      </c>
+      <c r="D10" t="str">
+        <v>출하요청수량</v>
+      </c>
+      <c r="E10" t="str">
+        <v>화면표시, 로직분기</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PACKING_QTY와 비교하여 계근 완료 판단, edit_wet_count UI 표시, centerTotalCount 합산</v>
+      </c>
+      <c r="G10" t="str">
+        <v>SM_출고상세.출고수량</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="str">
+        <v>GI_REQ_QTY</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ID.GI_REQ_QTY</v>
+      </c>
+      <c r="D11" t="str">
+        <v>출하요청중량</v>
+      </c>
+      <c r="E11" t="str">
+        <v>화면표시(진행률)</v>
+      </c>
+      <c r="F11" t="str">
+        <v>edit_wet_weight UI에 요청중량 표시, centerTotalWeight 합산 계산</v>
+      </c>
+      <c r="G11" t="str">
+        <v>SM_출고상세.출고중량</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" t="str">
+        <v>GI_REQ_DATE</v>
+      </c>
+      <c r="C12" t="str">
+        <v>GI_REQ_DATE</v>
+      </c>
+      <c r="D12" t="str">
+        <v>출하요청일</v>
+      </c>
+      <c r="E12" t="str">
+        <v>앱전달, 앱내미사용(로컬DB저장만)</v>
+      </c>
+      <c r="F12" t="str">
+        <v>JSP WHERE절에서 GI_REQ_DATE = Common.selectDay 조건 필터링. 앱 내부 로직에서 미사용, 로컬DB 저장만 됨</v>
+      </c>
+      <c r="G12" t="str">
+        <v>SM_출고상세.출고일자</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>20260310</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>8</v>
+      </c>
+      <c r="B13" t="str">
+        <v>BL_NO</v>
+      </c>
+      <c r="C13" t="str">
+        <v>DECODE(WR.BL_NO, NULL, WR.IMPORT_ID_NO, WR.BL_NO)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>BL번호(BL없으면 수입이력번호)</v>
+      </c>
+      <c r="E13" t="str">
+        <v>화면표시, 중복스캔방지</v>
+      </c>
+      <c r="F13" t="str">
+        <v>BL 스피너(sp_bl_no) 목록 구성, BL스캔 시 temp_bl_no와 비교하여 해당 상품 검색, 서버전송 패킷 포함</v>
+      </c>
+      <c r="G13" t="str">
+        <v>월품목별재고화일_LOT별_VIEW.BL_NO</v>
+      </c>
+      <c r="H13" t="str">
+        <v>이마트와 반대: BL_NO 우선, NULL이면 IMPORT_ID_NO (이마트는 IMPORT_ID_NO 우선)</v>
+      </c>
+      <c r="I13" t="str">
+        <v>BL2026030001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>9</v>
+      </c>
+      <c r="B14" t="str">
+        <v>BRAND_CODE</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ID.BRAND_CODE</v>
+      </c>
+      <c r="D14" t="str">
+        <v>브랜드코드</v>
+      </c>
+      <c r="E14" t="str">
+        <v>서버전송</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Goodswets_Info.setBRAND_CODE()로 저장, 서버전송 패킷 포함</v>
+      </c>
+      <c r="G14" t="str">
+        <v>?</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>BR01</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15" t="str">
+        <v>CLIENT_CODE</v>
+      </c>
+      <c r="C15" t="str">
+        <v>IH.CLIENT_CODE</v>
+      </c>
+      <c r="D15" t="str">
+        <v>출고업체코드</v>
+      </c>
+      <c r="E15" t="str">
+        <v>로직분기(DB조회조건)</v>
+      </c>
+      <c r="F15" t="str">
+        <v>DBHandler 조회 시 WHERE 조건으로 사용, Goodswets_Info에 저장</v>
+      </c>
+      <c r="G15" t="str">
+        <v>SM_출고머리.CLIENT_CODE</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>CL001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>11</v>
+      </c>
+      <c r="B16" t="str">
+        <v>CLIENTNAME</v>
+      </c>
+      <c r="C16" t="str">
+        <v>DE_CLIENT(IH.CLIENT_CODE)</v>
+      </c>
+      <c r="D16" t="str">
+        <v>출고업체명</v>
+      </c>
+      <c r="E16" t="str">
+        <v>화면표시</v>
+      </c>
+      <c r="F16" t="str">
+        <v>pointName으로 저장, 리스트 UI 표시 (si.CLIENTNAME)</v>
+      </c>
+      <c r="G16" t="str">
+        <v>CO_거래처.거래처명</v>
+      </c>
+      <c r="H16" t="str">
+        <v>이마트/홈플러스와 달리 DE_CLIENT() 함수 사용 (CJ 분기 없음)</v>
+      </c>
+      <c r="I16" t="str">
+        <v>롯데마트</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17" t="str">
+        <v>CENTERNAME</v>
+      </c>
+      <c r="C17" t="str">
+        <v>wmoi.CENTER_NAME (W_MART_ORDER_ITEM)</v>
+      </c>
+      <c r="D17" t="str">
+        <v>센터명</v>
+      </c>
+      <c r="E17" t="str">
+        <v>로직분기</v>
+      </c>
+      <c r="F17" t="str">
+        <v>CENTER_NAME_TRD/WET/ET 포함 여부 분기 판단 (BixolonShipmentActivity:747)</v>
+      </c>
+      <c r="G17" t="str">
+        <v>W_MART_ORDER_ITEM.CENTER_NAME</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>롯데마트 서울센터</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ITEM_SPEC</v>
+      </c>
+      <c r="C18" t="str">
+        <v>WR.ITEM_SPEC</v>
+      </c>
+      <c r="D18" t="str">
+        <v>상품규격</v>
+      </c>
+      <c r="E18" t="str">
+        <v>미사용(로컬DB저장만)</v>
+      </c>
+      <c r="F18" t="str">
+        <v>setPrintingLotte()에서 미사용. Goodswets_Info에 저장은 됨</v>
+      </c>
+      <c r="G18" t="str">
+        <v>CO_품목코드.규격</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>척아이롤/냉장</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" t="str">
+        <v>CT_CODE</v>
+      </c>
+      <c r="C19" t="str">
+        <v>id.CT_CODE</v>
+      </c>
+      <c r="D19" t="str">
+        <v>원산지코드</v>
+      </c>
+      <c r="E19" t="str">
+        <v>미사용(로컬DB저장만)</v>
+      </c>
+      <c r="F19" t="str">
+        <v>setPrintingLotte()에서 미사용. 로컬DB 저장만 됨</v>
+      </c>
+      <c r="G19" t="str">
+        <v>CO_품목코드.원산지</v>
+      </c>
+      <c r="H19" t="str">
+        <v>이마트와 달리 DECODE 없이 CT_CODE 그대로 반환 (원산지코드)</v>
+      </c>
+      <c r="I19" t="str">
+        <v>AU</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20" t="str">
+        <v>IMPORT_ID_NO</v>
+      </c>
+      <c r="C20" t="str">
+        <v>WR.IMPORT_ID_NO</v>
+      </c>
+      <c r="D20" t="str">
+        <v>수입식별번호</v>
+      </c>
+      <c r="E20" t="str">
+        <v>라벨출력</v>
+      </c>
+      <c r="F20" t="str">
+        <v>setPrintingLotte()에서 pBarcode2(이력번호바코드) 생성, 라벨 [10]이력(묶음)번호 출력 (LabelPrintHelper:1306,1407)</v>
+      </c>
+      <c r="G20" t="str">
+        <v>월품목별재고화일_LOT별_VIEW.이력번호</v>
+      </c>
+      <c r="H20" t="str">
+        <v>이마트와 달리 NVL 없음 (NULL 시 NPE 위험)</v>
+      </c>
+      <c r="I20" t="str">
+        <v>123456789012</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21" t="str">
+        <v>PACKER_CODE</v>
+      </c>
+      <c r="C21" t="str">
+        <v>[해외매입] BD.PACKER_CODE (I_BL_D) / [국내매입] OD.PACKER_CODE (I_OFFER_D)</v>
+      </c>
+      <c r="D21" t="str">
+        <v>패커코드</v>
+      </c>
+      <c r="E21" t="str">
+        <v>로직분기(킬코이30228)</v>
+      </c>
+      <c r="F21" t="str">
+        <v>KILKOY_PACKER_CODE("30228")와 비교하여 킬코이 제품 판별 로직 분기</v>
+      </c>
+      <c r="G21" t="str">
+        <v>CO_품목코드.가공장코드</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>30228</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>17</v>
+      </c>
+      <c r="B22" t="str">
+        <v>PACKER_PRODUCT_CODE</v>
+      </c>
+      <c r="C22" t="str">
+        <v>[해외매입] BD.PACKER_PRODUCT_CODE / [국내매입] OD.PACKER_PRODUCT_CODE</v>
+      </c>
+      <c r="D22" t="str">
+        <v>패커상품코드</v>
+      </c>
+      <c r="E22" t="str">
+        <v>화면표시, 서버전송</v>
+      </c>
+      <c r="F22" t="str">
+        <v>edit_product_code UI 표시, find_PackerProduct() 검색 기준, duplicatequeryGoodsWet() WHERE 조건, 서버전송 패킷 포함</v>
+      </c>
+      <c r="G22" t="str">
+        <v>CO_품목코드.PPCODE</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="B23" t="str">
+        <v>BARCODE_TYPE</v>
+      </c>
+      <c r="C23" t="str">
+        <v>beb.barcode_type (B_EMART_BARCODE, BARCODE_TYPE LIKE 'L%')</v>
+      </c>
+      <c r="D23" t="str">
+        <v>바코드타입</v>
+      </c>
+      <c r="E23" t="str">
+        <v>로직분기(라벨양식)</v>
+      </c>
+      <c r="F23" t="str">
+        <v>setPrintingLotte()에서 switch(BARCODE_TYPE) 분기 - 현재 L0 케이스만 구현됨 (LabelPrintHelper:1277)</v>
+      </c>
+      <c r="G23" t="str">
+        <v>CO_매출처품목코드매핑.바코드타입</v>
+      </c>
+      <c r="H23" t="str">
+        <v>JOIN 조건: BARCODE_TYPE LIKE 'L%' (이마트는 ITEM_TYPE='W' 조건)</v>
+      </c>
+      <c r="I23" t="str">
+        <v>L0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>19</v>
+      </c>
+      <c r="B24" t="str">
+        <v>ITEM_TYPE</v>
+      </c>
+      <c r="C24" t="str">
+        <v>'S' 하드코딩 (VIEW에서 고정)</v>
+      </c>
+      <c r="D24" t="str">
+        <v>아이템타입</v>
+      </c>
+      <c r="E24" t="str">
+        <v>로직분기(계근방식)</v>
+      </c>
+      <c r="F24" t="str">
+        <v>setPrintingLotte()에서 W/S/J 분기 존재, VIEW에서 항상 S 고정이므로 W/S 분기 진입. J타입(제품계근) 미발생</v>
+      </c>
+      <c r="G24" t="str">
+        <v>고정값</v>
+      </c>
+      <c r="H24" t="str">
+        <v>VIEW에서 S 하드코딩. ITEM_TYPE=J 분기 미진입</v>
+      </c>
+      <c r="I24" t="str">
+        <v>S</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>20</v>
+      </c>
+      <c r="B25" t="str">
+        <v>PACKWEIGHT</v>
+      </c>
+      <c r="C25" t="str">
+        <v>NULL 하드코딩 (VIEW에서 고정)</v>
+      </c>
+      <c r="D25" t="str">
+        <v>포장중량</v>
+      </c>
+      <c r="E25" t="str">
+        <v>미사용(NULL고정)</v>
+      </c>
+      <c r="F25" t="str">
+        <v>ITEM_TYPE=J 시 setPrintingLotte()에서 사용하나, VIEW에서 NULL 고정으로 J타입 계근 미발생</v>
+      </c>
+      <c r="G25" t="str">
+        <v>CO_품목코드.박스중량</v>
+      </c>
+      <c r="H25" t="str">
+        <v>VIEW에서 NULL 하드코딩</v>
+      </c>
+      <c r="I25" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>21</v>
+      </c>
+      <c r="B26" t="str">
+        <v>BARCODEGOODS</v>
+      </c>
+      <c r="C26" t="str">
+        <v>[해외매입] SELECT BARCODEGOODS FROM S_BARCODE_INFO WHERE PACKER_CLIENT_CODE=BD.PACKER_CODE AND PACKER_PRODUCT_CODE=BD.PACKER_PRODUCT_CODE AND STATUS='Y' / [국내매입] 동일 OD 기준</v>
+      </c>
+      <c r="D26" t="str">
+        <v>바코드상품코드</v>
+      </c>
+      <c r="E26" t="str">
+        <v>아이템검색</v>
+      </c>
+      <c r="F26" t="str">
+        <v>find_PackerProductBarcodeGoods()에서 스캔 바코드와 비교하여 상품 매칭, work_item_barcodegoods에 저장</v>
+      </c>
+      <c r="G26" t="str">
+        <v>CO_품목코드.상품바코드</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>22</v>
+      </c>
+      <c r="B27" t="str">
+        <v>STORE_IN_DATE</v>
+      </c>
+      <c r="C27" t="str">
+        <v>WR.FROM_EXPIRY_DATE</v>
+      </c>
+      <c r="D27" t="str">
+        <v>유통기한 시작일</v>
+      </c>
+      <c r="E27" t="str">
+        <v>미사용(로컬DB저장만)</v>
+      </c>
+      <c r="F27" t="str">
+        <v>setPrintingLotte()에서 미사용 (제조일자는 스캔 바코드에서 파싱). Goodswets_Info에 저장만 됨</v>
+      </c>
+      <c r="G27" t="str">
+        <v>SM_수주상세.납기일자</v>
+      </c>
+      <c r="H27" t="str">
+        <v>이마트(W_E_ORDER_ITEM.STORE_IN_DATE)와 달리 W_GOODS_R.FROM_EXPIRY_DATE 사용</v>
+      </c>
+      <c r="I27" t="str">
+        <v>20260310</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>23</v>
+      </c>
+      <c r="B28" t="str">
+        <v>EMARTLOGIS_CODE</v>
+      </c>
+      <c r="C28" t="str">
+        <v>B_COMMON_CODE (MASTER_CODE='LOTTE_STORE_CODE', code=wmoi.CENTER_CODE).REF_CODE2</v>
+      </c>
+      <c r="D28" t="str">
+        <v>롯데 회사코드</v>
+      </c>
+      <c r="E28" t="str">
+        <v>라벨바코드</v>
+      </c>
+      <c r="F28" t="str">
+        <v>setPrintingLotte()에서 pCompCode_lotte로 저장, L0 중량바코드 앞부분 생성에 사용 (LabelPrintHelper:1199,1301)</v>
+      </c>
+      <c r="G28" t="str">
+        <v>W_MART_ORDER_ITEM 기반 B_COMMON_CODE.REF_CODE2</v>
+      </c>
+      <c r="H28" t="str">
+        <v>홈플러스(EO.STORECODE)와 달리 B_COMMON_CODE.REF_CODE2 반환 (롯데 회사코드)</v>
+      </c>
+      <c r="I28" t="str">
+        <v>610933</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>24</v>
+      </c>
+      <c r="B29" t="str">
+        <v>WH_AREA</v>
+      </c>
+      <c r="C29" t="str">
+        <v>'' 빈 문자열 하드코딩 (VIEW에서 고정)</v>
+      </c>
+      <c r="D29" t="str">
+        <v>창고구역</v>
+      </c>
+      <c r="E29" t="str">
+        <v>미사용(빈값고정)</v>
+      </c>
+      <c r="F29" t="str">
+        <v>setPrintingLotte()에서 라벨 [11]WH_AREA 출력 시도하나 VIEW에서 항상 빈 문자열 고정으로 라벨에 미출력</v>
+      </c>
+      <c r="G29" t="str">
+        <v>고정값</v>
+      </c>
+      <c r="H29" t="str">
+        <v>VIEW에서 '' 하드코딩. 실제 창고구역 미적용</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>25</v>
+      </c>
+      <c r="B30" t="str">
+        <v>LAST_BOX_ORDER</v>
+      </c>
+      <c r="C30" t="str">
+        <v>W_GOODS_WET.BOX_ORDER 서브쿼리 (최근 정상 마지막 박스순번 추출, 연속성 및 9999 로테이션 검사)</v>
+      </c>
+      <c r="D30" t="str">
+        <v>마지막 박스순번</v>
+      </c>
+      <c r="E30" t="str">
+        <v>로직분기(박스순번계산)</v>
+      </c>
+      <c r="F30" t="str">
+        <v>BixolonShipmentActivity에서 이전 박스순번 기반으로 다음 box_order 계산 후 setPrintingLotte() 파라미터로 전달</v>
+      </c>
+      <c r="G30" t="str">
+        <v>TB_GOODS_WET.BOX_ORDER</v>
+      </c>
+      <c r="H30" t="str">
+        <v>1~9999 순환. 이전 계근의 정상 순번을 추출하여 연속성 검증</v>
+      </c>
+      <c r="I30" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>-</v>
+      </c>
+      <c r="B31" t="str">
+        <v>GR_WAREHOUSE_CODE</v>
+      </c>
+      <c r="C31" t="str">
+        <v>WR.GR_WAREHOUSE_CODE</v>
+      </c>
+      <c r="D31" t="str">
+        <v>창고코드</v>
+      </c>
+      <c r="E31" t="str">
+        <v>JSP미전달(WHERE조건용)</v>
+      </c>
+      <c r="F31" t="str">
+        <v>VIEW에 존재하나 JSP SELECT 미포함, ProgressDlgShipSearch WHERE 조건(GR_WAREHOUSE_CODE='IN10273' 등)으로만 사용</v>
+      </c>
+      <c r="G31" t="str">
+        <v>SM_출고상세.창고코드</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>WH01</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I31"/>
+  </ignoredErrors>
+</worksheet>
 </file>